--- a/price_check_links.xlsx
+++ b/price_check_links.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11625"/>
+    <workbookView windowWidth="12885" windowHeight="11610"/>
   </bookViews>
   <sheets>
     <sheet name="input_products" sheetId="1" r:id="rId1"/>
